--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484215_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484215_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.2368</v>
+        <v>3.548</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5171</v>
+        <v>0.7194</v>
       </c>
       <c r="F2" t="n">
-        <v>2.7196</v>
+        <v>2.8286</v>
       </c>
       <c r="G2" t="n">
         <v>-0.8641</v>
@@ -610,13 +610,13 @@
         <v>2.3441</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7605</v>
+        <v>1.0717</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7567</v>
+        <v>0.959</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0038</v>
+        <v>0.1127</v>
       </c>
       <c r="V2" t="n">
         <v>0.9962</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>G. HERETER MARCHANTE</t>
+          <t>P. CARRIÓN SORIANO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.7408</v>
+        <v>2.6321</v>
       </c>
       <c r="E3" t="n">
-        <v>3.4125</v>
+        <v>2.6291</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.6718</v>
+        <v>0.003</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7566000000000001</v>
+        <v>2.1599</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3118</v>
+        <v>0.9197</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4447</v>
+        <v>1.2402</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6365</v>
+        <v>3.3892</v>
       </c>
       <c r="K3" t="n">
-        <v>0.596</v>
+        <v>0.7994</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0405</v>
+        <v>2.5898</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1201</v>
+        <v>-1.2293</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.2842</v>
+        <v>0.1203</v>
       </c>
       <c r="O3" t="n">
-        <v>0.4043</v>
+        <v>-1.3496</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.9767</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q3" t="n">
         <v>-1.9534</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9767</v>
+        <v>1.7581</v>
       </c>
       <c r="S3" t="n">
-        <v>2.6837</v>
+        <v>-0.152</v>
       </c>
       <c r="T3" t="n">
-        <v>2.347</v>
+        <v>-0.0254</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3366</v>
+        <v>-0.1267</v>
       </c>
       <c r="V3" t="n">
-        <v>0.2772</v>
+        <v>0.8195</v>
       </c>
       <c r="W3" t="n">
-        <v>2.3824</v>
+        <v>1.2186</v>
       </c>
       <c r="X3" t="n">
-        <v>-2.1052</v>
+        <v>-0.3991</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. ABELLO GIRVÉS</t>
+          <t>A. RECIO PIÑOL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.2565</v>
+        <v>1.7595</v>
       </c>
       <c r="E4" t="n">
-        <v>2.7043</v>
+        <v>0.7629</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.4478</v>
+        <v>0.9966</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.8159</v>
+        <v>-0.9199000000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3446</v>
+        <v>0.3479</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.1605</v>
+        <v>-1.2679</v>
       </c>
       <c r="J4" t="n">
-        <v>1.2272</v>
+        <v>0.1039</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4988</v>
+        <v>0.6971000000000001</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7284</v>
+        <v>-0.5931999999999999</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.0431</v>
+        <v>-1.0239</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.1542</v>
+        <v>-0.3492</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.8889</v>
+        <v>-0.6747</v>
       </c>
       <c r="P4" t="n">
-        <v>0.586</v>
+        <v>0.1953</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R4" t="n">
-        <v>2.5395</v>
+        <v>1.1721</v>
       </c>
       <c r="S4" t="n">
-        <v>2.3189</v>
+        <v>0.9334</v>
       </c>
       <c r="T4" t="n">
-        <v>2.0444</v>
+        <v>0.7491</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2744</v>
+        <v>0.1843</v>
       </c>
       <c r="V4" t="n">
-        <v>0.1675</v>
+        <v>1.5507</v>
       </c>
       <c r="W4" t="n">
-        <v>1.3862</v>
+        <v>0.8865</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.2186</v>
+        <v>0.6642</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P. CARRIÓN SORIANO</t>
+          <t>F. VILAR FERNANDEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.181</v>
+        <v>1.6834</v>
       </c>
       <c r="E5" t="n">
-        <v>2.1235</v>
+        <v>3.6676</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0574</v>
+        <v>-1.9842</v>
       </c>
       <c r="G5" t="n">
-        <v>2.1599</v>
+        <v>3.6527</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9197</v>
+        <v>4.7324</v>
       </c>
       <c r="I5" t="n">
-        <v>1.2402</v>
+        <v>-1.0797</v>
       </c>
       <c r="J5" t="n">
-        <v>3.3892</v>
+        <v>5.5612</v>
       </c>
       <c r="K5" t="n">
-        <v>0.7994</v>
+        <v>4.7519</v>
       </c>
       <c r="L5" t="n">
-        <v>2.5898</v>
+        <v>0.8093</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.2293</v>
+        <v>-1.9085</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1203</v>
+        <v>-0.0194</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.3496</v>
+        <v>-1.8891</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.1953</v>
+        <v>-1.3674</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.9534</v>
+        <v>-2.9301</v>
       </c>
       <c r="R5" t="n">
-        <v>1.7581</v>
+        <v>1.5627</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.6031</v>
+        <v>0.1293</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5309</v>
+        <v>0.1501</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0722</v>
+        <v>-0.0208</v>
       </c>
       <c r="V5" t="n">
-        <v>0.8195</v>
+        <v>-0.7312</v>
       </c>
       <c r="W5" t="n">
-        <v>1.2186</v>
+        <v>0.8865</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.3991</v>
+        <v>-1.6177</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>F. VILAR FERNANDEZ</t>
+          <t>A. ABELLO GIRVÉS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2905</v>
+        <v>1.0547</v>
       </c>
       <c r="E6" t="n">
-        <v>3.4654</v>
+        <v>1.6932</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.1749</v>
+        <v>-0.6385</v>
       </c>
       <c r="G6" t="n">
-        <v>3.6527</v>
+        <v>-0.8159</v>
       </c>
       <c r="H6" t="n">
-        <v>4.7324</v>
+        <v>0.3446</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.0797</v>
+        <v>-1.1605</v>
       </c>
       <c r="J6" t="n">
-        <v>5.5612</v>
+        <v>1.2272</v>
       </c>
       <c r="K6" t="n">
-        <v>4.7519</v>
+        <v>0.4988</v>
       </c>
       <c r="L6" t="n">
-        <v>0.8093</v>
+        <v>0.7284</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.9085</v>
+        <v>-2.0431</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.0194</v>
+        <v>-0.1542</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.8891</v>
+        <v>-1.8889</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.3674</v>
+        <v>0.586</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.9301</v>
+        <v>-1.9534</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5627</v>
+        <v>2.5395</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2636</v>
+        <v>1.1171</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0522</v>
+        <v>1.0333</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2114</v>
+        <v>0.0838</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.7312</v>
+        <v>0.1675</v>
       </c>
       <c r="W6" t="n">
-        <v>0.8865</v>
+        <v>1.3862</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.6177</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. RECIO PIÑOL</t>
+          <t>G. HERETER MARCHANTE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.1838</v>
+        <v>1.0256</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4596</v>
+        <v>1.9969</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7243000000000001</v>
+        <v>-0.9714</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.9199000000000001</v>
+        <v>0.7566000000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3479</v>
+        <v>0.3118</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.2679</v>
+        <v>0.4447</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1039</v>
+        <v>0.6365</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6971000000000001</v>
+        <v>0.596</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.5931999999999999</v>
+        <v>0.0405</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.0239</v>
+        <v>0.1201</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.3492</v>
+        <v>-0.2842</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.6747</v>
+        <v>0.4043</v>
       </c>
       <c r="P7" t="n">
-        <v>0.1953</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1721</v>
+        <v>0.9767</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3577</v>
+        <v>0.9685</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4458</v>
+        <v>0.9314</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0881</v>
+        <v>0.037</v>
       </c>
       <c r="V7" t="n">
-        <v>1.5507</v>
+        <v>0.2772</v>
       </c>
       <c r="W7" t="n">
-        <v>0.8865</v>
+        <v>2.3824</v>
       </c>
       <c r="X7" t="n">
-        <v>0.6642</v>
+        <v>-2.1052</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. GARCIA RODRIGUEZ</t>
+          <t>A. JAIME BATLLE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0221</v>
+        <v>0.7514999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1869</v>
+        <v>0.7425</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1648</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.3593</v>
+        <v>1.2833</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.4671</v>
+        <v>-0.9824000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1078</v>
+        <v>2.2657</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0552</v>
+        <v>2.9971</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.5921999999999999</v>
+        <v>-0.7534</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6475</v>
+        <v>3.7505</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.4146</v>
+        <v>-1.7137</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1251</v>
+        <v>-0.2289</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.5397</v>
+        <v>-1.4848</v>
       </c>
       <c r="P8" t="n">
-        <v>0.586</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.9534</v>
       </c>
       <c r="R8" t="n">
-        <v>0.586</v>
+        <v>1.9534</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2488</v>
+        <v>-0.41</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2421</v>
+        <v>-0.3012</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0067</v>
+        <v>-0.1088</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-0.1219</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.1219</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. JAIME BATLLE</t>
+          <t>P. GARCIA RODRIGUEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1548</v>
+        <v>0.2734</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1358</v>
+        <v>0.2176</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.2906</v>
+        <v>0.0558</v>
       </c>
       <c r="G9" t="n">
-        <v>1.2833</v>
+        <v>-0.3593</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.9824000000000001</v>
+        <v>-0.4671</v>
       </c>
       <c r="I9" t="n">
-        <v>2.2657</v>
+        <v>0.1078</v>
       </c>
       <c r="J9" t="n">
-        <v>2.9971</v>
+        <v>0.0552</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.7534</v>
+        <v>-0.5921999999999999</v>
       </c>
       <c r="L9" t="n">
-        <v>3.7505</v>
+        <v>0.6475</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.7137</v>
+        <v>-0.4146</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.2289</v>
+        <v>0.1251</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.4848</v>
+        <v>-0.5397</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>0.586</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.9534</v>
+        <v>0.586</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.3163</v>
+        <v>0.0467</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.9078000000000001</v>
+        <v>0.1624</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4084</v>
+        <v>-0.1156</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.1219</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.1219</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.0911</v>
+        <v>-1.5657</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.283</v>
+        <v>-0.4852</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.8081</v>
+        <v>-1.0804</v>
       </c>
       <c r="G10" t="n">
         <v>0.7739</v>
@@ -1234,13 +1234,13 @@
         <v>0.9767</v>
       </c>
       <c r="S10" t="n">
-        <v>0.5777</v>
+        <v>0.1031</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1899</v>
+        <v>-0.0123</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3878</v>
+        <v>0.1154</v>
       </c>
       <c r="V10" t="n">
         <v>0.4875</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. SUAREZ CANOSA</t>
+          <t>S. IBORRA BARRERA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.4431</v>
+        <v>-2.0571</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1721</v>
+        <v>-0.7571</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.6152</v>
+        <v>-1.3</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.6126</v>
+        <v>-0.9167999999999999</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1023</v>
+        <v>0.8631</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.715</v>
+        <v>-1.7799</v>
       </c>
       <c r="J11" t="n">
-        <v>0.137</v>
+        <v>-0.6368</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0422</v>
+        <v>0.738</v>
       </c>
       <c r="L11" t="n">
-        <v>0.09470000000000001</v>
+        <v>-1.3748</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.7496</v>
+        <v>-0.2799</v>
       </c>
       <c r="N11" t="n">
-        <v>0.0601</v>
+        <v>0.1251</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.8097</v>
+        <v>-0.4051</v>
       </c>
       <c r="P11" t="n">
-        <v>0.1953</v>
+        <v>0.586</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.1953</v>
+        <v>0.586</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1342</v>
+        <v>-0.3859</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2421</v>
+        <v>-0.1203</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3763</v>
+        <v>-0.2656</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.16</v>
+        <v>-1.3405</v>
       </c>
       <c r="W11" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.4373</v>
+        <v>-1.3405</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>S. IBORRA BARRERA</t>
+          <t>M. SUAREZ CANOSA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.6056</v>
+        <v>-2.5327</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.0605</v>
+        <v>0.2732</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.5451</v>
+        <v>-2.8059</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.9167999999999999</v>
+        <v>-0.6126</v>
       </c>
       <c r="H12" t="n">
-        <v>0.8631</v>
+        <v>0.1023</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.7799</v>
+        <v>-0.715</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.6368</v>
+        <v>0.137</v>
       </c>
       <c r="K12" t="n">
-        <v>0.738</v>
+        <v>0.0422</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.3748</v>
+        <v>0.09470000000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.2799</v>
+        <v>-0.7496</v>
       </c>
       <c r="N12" t="n">
-        <v>0.1251</v>
+        <v>0.0601</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.4051</v>
+        <v>-0.8097</v>
       </c>
       <c r="P12" t="n">
-        <v>0.586</v>
+        <v>0.1953</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0.586</v>
+        <v>0.1953</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.9343</v>
+        <v>0.0447</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4237</v>
+        <v>-0.141</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.5107</v>
+        <v>0.1856</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.3405</v>
+        <v>-2.16</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.3405</v>
+        <v>-2.4373</v>
       </c>
     </row>
     <row r="13">
@@ -1423,16 +1423,16 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.572700000000002</v>
+        <v>6.572699999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>11.4599</v>
+        <v>11.4601</v>
       </c>
       <c r="F13" t="n">
         <v>-4.8874</v>
       </c>
       <c r="G13" t="n">
-        <v>4.1378</v>
+        <v>4.137799999999999</v>
       </c>
       <c r="H13" t="n">
         <v>8.186199999999999</v>
@@ -1459,7 +1459,7 @@
         <v>-10.7966</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.9768000000000002</v>
+        <v>-0.9767999999999999</v>
       </c>
       <c r="Q13" t="n">
         <v>-15.6273</v>
@@ -1471,16 +1471,16 @@
         <v>3.4666</v>
       </c>
       <c r="T13" t="n">
-        <v>3.384999999999999</v>
+        <v>3.3851</v>
       </c>
       <c r="U13" t="n">
-        <v>0.08140000000000003</v>
+        <v>0.08129999999999996</v>
       </c>
       <c r="V13" t="n">
         <v>-0.05500000000000016</v>
       </c>
       <c r="W13" t="n">
-        <v>7.923899999999999</v>
+        <v>7.9239</v>
       </c>
       <c r="X13" t="n">
         <v>-7.978999999999999</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. MURCIANO PUJADAS</t>
+          <t>A. VIÑALLONGA GOMEZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.3993</v>
+        <v>2.8556</v>
       </c>
       <c r="E14" t="n">
-        <v>2.9774</v>
+        <v>3.4349</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.5780999999999999</v>
+        <v>-0.5794</v>
       </c>
       <c r="G14" t="n">
-        <v>0.3273</v>
+        <v>3.4756</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.3448</v>
+        <v>-1.1655</v>
       </c>
       <c r="I14" t="n">
-        <v>1.6721</v>
+        <v>4.6411</v>
       </c>
       <c r="J14" t="n">
-        <v>3.2633</v>
+        <v>5.9422</v>
       </c>
       <c r="K14" t="n">
-        <v>0.5116000000000001</v>
+        <v>0.4912</v>
       </c>
       <c r="L14" t="n">
-        <v>2.7517</v>
+        <v>5.451</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.936</v>
+        <v>-2.4666</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.8565</v>
+        <v>-1.6567</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.0795</v>
+        <v>-0.8099</v>
       </c>
       <c r="P14" t="n">
-        <v>0.586</v>
+        <v>-1.5627</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.9534</v>
+        <v>-4.1022</v>
       </c>
       <c r="R14" t="n">
         <v>2.5395</v>
       </c>
       <c r="S14" t="n">
-        <v>2.0405</v>
+        <v>-0.3308</v>
       </c>
       <c r="T14" t="n">
-        <v>1.6675</v>
+        <v>-0.233</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3729</v>
+        <v>-0.0978</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.5545</v>
+        <v>1.2735</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.8279</v>
       </c>
       <c r="X14" t="n">
         <v>-0.5545</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. VIÑALLONGA GOMEZ</t>
+          <t>G. PRAT PRUNA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.3071</v>
+        <v>1.0974</v>
       </c>
       <c r="E15" t="n">
-        <v>3.1316</v>
+        <v>1.715</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.8245</v>
+        <v>-0.6175</v>
       </c>
       <c r="G15" t="n">
-        <v>3.4756</v>
+        <v>-2.232</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.1655</v>
+        <v>0.1</v>
       </c>
       <c r="I15" t="n">
-        <v>4.6411</v>
+        <v>-2.332</v>
       </c>
       <c r="J15" t="n">
-        <v>5.9422</v>
+        <v>0.5741000000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>0.4912</v>
+        <v>1.8265</v>
       </c>
       <c r="L15" t="n">
-        <v>5.451</v>
+        <v>-1.2525</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.4666</v>
+        <v>-2.8061</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.6567</v>
+        <v>-1.7265</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.8099</v>
+        <v>-1.0795</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.5627</v>
+        <v>1.3674</v>
       </c>
       <c r="Q15" t="n">
-        <v>-4.1022</v>
+        <v>-1.1721</v>
       </c>
       <c r="R15" t="n">
         <v>2.5395</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.8792</v>
+        <v>-0.7524999999999999</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.5364</v>
+        <v>-0.4015</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3429</v>
+        <v>-0.3509</v>
       </c>
       <c r="V15" t="n">
-        <v>1.2735</v>
+        <v>2.7145</v>
       </c>
       <c r="W15" t="n">
-        <v>1.8279</v>
+        <v>2.7145</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.5545</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>G. PRAT PRUNA</t>
+          <t>A. MURCIANO PUJADAS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1809</v>
+        <v>0.8397</v>
       </c>
       <c r="E16" t="n">
-        <v>0.906</v>
+        <v>1.6629</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.7251</v>
+        <v>-0.8232</v>
       </c>
       <c r="G16" t="n">
-        <v>-2.232</v>
+        <v>0.3273</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1</v>
+        <v>-1.3448</v>
       </c>
       <c r="I16" t="n">
-        <v>-2.332</v>
+        <v>1.6721</v>
       </c>
       <c r="J16" t="n">
-        <v>0.5741000000000001</v>
+        <v>3.2633</v>
       </c>
       <c r="K16" t="n">
-        <v>1.8265</v>
+        <v>0.5116000000000001</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.2525</v>
+        <v>2.7517</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.8061</v>
+        <v>-2.936</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.7265</v>
+        <v>-1.8565</v>
       </c>
       <c r="O16" t="n">
         <v>-1.0795</v>
       </c>
       <c r="P16" t="n">
-        <v>1.3674</v>
+        <v>0.586</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1721</v>
+        <v>-1.9534</v>
       </c>
       <c r="R16" t="n">
         <v>2.5395</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.669</v>
+        <v>0.4808</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.2105</v>
+        <v>0.353</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4585</v>
+        <v>0.1278</v>
       </c>
       <c r="V16" t="n">
-        <v>2.7145</v>
+        <v>-0.5545</v>
       </c>
       <c r="W16" t="n">
-        <v>2.7145</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.5545</v>
       </c>
     </row>
     <row r="17">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.09080000000000001</v>
+        <v>-0.1088</v>
       </c>
       <c r="E18" t="n">
-        <v>1.7229</v>
+        <v>1.1162</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.6321</v>
+        <v>-1.2249</v>
       </c>
       <c r="G18" t="n">
         <v>0.4539</v>
@@ -1858,13 +1858,13 @@
         <v>0.3907</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.7538</v>
+        <v>-0.9533</v>
       </c>
       <c r="T18" t="n">
-        <v>0.6824</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.4363</v>
+        <v>-1.0291</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>C. HOMS LORENZO</t>
+          <t>O. HERAS FLECHA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.143</v>
+        <v>-0.6329</v>
       </c>
       <c r="E19" t="n">
-        <v>0.7095</v>
+        <v>1.3547</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.8526</v>
+        <v>-1.9876</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.3521</v>
+        <v>5.0028</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.7872</v>
+        <v>0.4705</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.5649</v>
+        <v>4.5324</v>
       </c>
       <c r="J19" t="n">
-        <v>0.5744</v>
+        <v>5.4417</v>
       </c>
       <c r="K19" t="n">
-        <v>0.2507</v>
+        <v>1.0438</v>
       </c>
       <c r="L19" t="n">
-        <v>0.3237</v>
+        <v>4.3979</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.9265</v>
+        <v>-0.4388</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.0379</v>
+        <v>-0.5733</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.8887</v>
+        <v>0.1344</v>
       </c>
       <c r="P19" t="n">
-        <v>1.7581</v>
+        <v>-2.7348</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1721</v>
+        <v>-3.9069</v>
       </c>
       <c r="R19" t="n">
-        <v>2.9301</v>
+        <v>1.1721</v>
       </c>
       <c r="S19" t="n">
-        <v>1.7245</v>
+        <v>-1.073</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1983</v>
+        <v>-0.1801</v>
       </c>
       <c r="U19" t="n">
-        <v>1.5262</v>
+        <v>-0.8929</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.2735</v>
+        <v>-1.8279</v>
       </c>
       <c r="W19" t="n">
-        <v>1.1089</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.3824</v>
+        <v>-1.8279</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>O. HERAS FLECHA</t>
+          <t>C. HOMS LORENZO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.7285</v>
+        <v>-1.0806</v>
       </c>
       <c r="E20" t="n">
-        <v>0.748</v>
+        <v>0.5073</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.4765</v>
+        <v>-1.5879</v>
       </c>
       <c r="G20" t="n">
-        <v>5.0028</v>
+        <v>-2.3521</v>
       </c>
       <c r="H20" t="n">
-        <v>0.4705</v>
+        <v>-0.7872</v>
       </c>
       <c r="I20" t="n">
-        <v>4.5324</v>
+        <v>-1.5649</v>
       </c>
       <c r="J20" t="n">
-        <v>5.4417</v>
+        <v>0.5744</v>
       </c>
       <c r="K20" t="n">
-        <v>1.0438</v>
+        <v>0.2507</v>
       </c>
       <c r="L20" t="n">
-        <v>4.3979</v>
+        <v>0.3237</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.4388</v>
+        <v>-2.9265</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.5733</v>
+        <v>-1.0379</v>
       </c>
       <c r="O20" t="n">
-        <v>0.1344</v>
+        <v>-1.8887</v>
       </c>
       <c r="P20" t="n">
-        <v>-2.7348</v>
+        <v>1.7581</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.9069</v>
+        <v>-1.1721</v>
       </c>
       <c r="R20" t="n">
-        <v>1.1721</v>
+        <v>2.9301</v>
       </c>
       <c r="S20" t="n">
-        <v>-2.1686</v>
+        <v>0.7869</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7868000000000001</v>
+        <v>-0.004</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.3818</v>
+        <v>0.7909</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.8279</v>
+        <v>-1.2735</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.1089</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.8279</v>
+        <v>-2.3824</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.9376</v>
+        <v>-2.0788</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.2133</v>
+        <v>-1.5166</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.7243000000000001</v>
+        <v>-0.5622</v>
       </c>
       <c r="G21" t="n">
         <v>-1.2273</v>
@@ -2092,13 +2092,13 @@
         <v>0.9767</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2377</v>
+        <v>-0.379</v>
       </c>
       <c r="T21" t="n">
-        <v>0.6219</v>
+        <v>0.3186</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.8596</v>
+        <v>-0.6976</v>
       </c>
       <c r="V21" t="n">
         <v>-0.2772</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. BALLÚS TORRAS</t>
+          <t>M. SALMERON SEGU</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.4746</v>
+        <v>-2.1547</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.7346</v>
+        <v>-1.7451</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.7399</v>
+        <v>-0.4096</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.0788</v>
+        <v>-5.1224</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.6741</v>
+        <v>-2.5869</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.4047</v>
+        <v>-2.5355</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.6741</v>
+        <v>-2.4706</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.6741</v>
+        <v>-1.2843</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>-1.1863</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.4047</v>
+        <v>-2.6518</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>-1.3026</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.4047</v>
+        <v>-1.3492</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>0.9767</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-1.1721</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2.1488</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1772</v>
+        <v>0.1631</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0605</v>
+        <v>0.0696</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1167</v>
+        <v>0.0935</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.2186</v>
+        <v>1.8279</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.8279</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>M. SALMERON SEGU</t>
+          <t>A. PEIRO COSMO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.6759</v>
+        <v>-2.3634</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.0485</v>
+        <v>-0.8873</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.6274</v>
+        <v>-1.4761</v>
       </c>
       <c r="G23" t="n">
-        <v>-5.1224</v>
+        <v>-1.4253</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.5869</v>
+        <v>-1.6408</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.5355</v>
+        <v>0.2156</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.4706</v>
+        <v>-1.2059</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.2843</v>
+        <v>-1.2868</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.1863</v>
+        <v>0.0809</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.6518</v>
+        <v>-0.2194</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.3026</v>
+        <v>-0.354</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.3492</v>
+        <v>0.1346</v>
       </c>
       <c r="P23" t="n">
-        <v>0.9767</v>
+        <v>0.1953</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.1721</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>2.1488</v>
+        <v>0.1953</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.3581</v>
+        <v>-0.5241</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2337</v>
+        <v>0.0413</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1244</v>
+        <v>-0.5655</v>
       </c>
       <c r="V23" t="n">
-        <v>1.8279</v>
+        <v>-0.6093</v>
       </c>
       <c r="W23" t="n">
-        <v>1.8279</v>
+        <v>0.2772</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-0.8865</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A. PEIRO COSMO</t>
+          <t>M. BALLÚS TORRAS</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.7665</v>
+        <v>-2.4473</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.2918</v>
+        <v>-0.7346</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.4747</v>
+        <v>-1.7127</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.4253</v>
+        <v>-1.0788</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.6408</v>
+        <v>-0.6741</v>
       </c>
       <c r="I24" t="n">
-        <v>0.2156</v>
+        <v>-0.4047</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.2059</v>
+        <v>-0.6741</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.2868</v>
+        <v>-0.6741</v>
       </c>
       <c r="L24" t="n">
-        <v>0.0809</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.2194</v>
+        <v>-0.4047</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.354</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>0.1346</v>
+        <v>-0.4047</v>
       </c>
       <c r="P24" t="n">
-        <v>0.1953</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>0.1953</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.9273</v>
+        <v>-0.15</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.3631</v>
+        <v>-0.0605</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.5641</v>
+        <v>-0.08939999999999999</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.6093</v>
+        <v>-1.2186</v>
       </c>
       <c r="W24" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.8865</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.572699999999999</v>
+        <v>-5.8985</v>
       </c>
       <c r="E25" t="n">
-        <v>4.887099999999998</v>
+        <v>4.887300000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>-11.4599</v>
+        <v>-10.7858</v>
       </c>
       <c r="G25" t="n">
         <v>-4.1378</v>
@@ -2374,13 +2374,13 @@
         <v>-8.186199999999999</v>
       </c>
       <c r="I25" t="n">
-        <v>4.048700000000001</v>
+        <v>4.0487</v>
       </c>
       <c r="J25" t="n">
         <v>11.6405</v>
       </c>
       <c r="K25" t="n">
-        <v>0.8439999999999999</v>
+        <v>0.844</v>
       </c>
       <c r="L25" t="n">
         <v>10.7964</v>
@@ -2395,7 +2395,7 @@
         <v>-6.748</v>
       </c>
       <c r="P25" t="n">
-        <v>0.9767000000000001</v>
+        <v>0.9766999999999999</v>
       </c>
       <c r="Q25" t="n">
         <v>-14.6509</v>
@@ -2404,16 +2404,16 @@
         <v>15.6275</v>
       </c>
       <c r="S25" t="n">
-        <v>-3.4664</v>
+        <v>-2.792399999999999</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.08139999999999992</v>
+        <v>-0.08130000000000009</v>
       </c>
       <c r="U25" t="n">
-        <v>-3.3852</v>
+        <v>-2.711</v>
       </c>
       <c r="V25" t="n">
-        <v>0.05490000000000017</v>
+        <v>0.05490000000000061</v>
       </c>
       <c r="W25" t="n">
         <v>7.978800000000001</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484215_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484215_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -558,7 +563,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -626,240 +631,260 @@
       </c>
       <c r="X2" t="n">
         <v>0.3869</v>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484215_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>P. CARRIÓN SORIANO</t>
+          <t>F. VILAR FERNANDEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.6321</v>
+        <v>1.6834</v>
       </c>
       <c r="E3" t="n">
-        <v>2.6291</v>
+        <v>3.6676</v>
       </c>
       <c r="F3" t="n">
-        <v>0.003</v>
+        <v>-1.9842</v>
       </c>
       <c r="G3" t="n">
-        <v>2.1599</v>
+        <v>3.6527</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9197</v>
+        <v>4.7324</v>
       </c>
       <c r="I3" t="n">
-        <v>1.2402</v>
+        <v>-1.0797</v>
       </c>
       <c r="J3" t="n">
-        <v>3.3892</v>
+        <v>5.5612</v>
       </c>
       <c r="K3" t="n">
-        <v>0.7994</v>
+        <v>4.7519</v>
       </c>
       <c r="L3" t="n">
-        <v>2.5898</v>
+        <v>0.8093</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.2293</v>
+        <v>-1.9085</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1203</v>
+        <v>-0.0194</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.3496</v>
+        <v>-1.8891</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.1953</v>
+        <v>-1.3674</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.9534</v>
+        <v>-2.9301</v>
       </c>
       <c r="R3" t="n">
-        <v>1.7581</v>
+        <v>1.5627</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.152</v>
+        <v>0.1293</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.0254</v>
+        <v>0.1501</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1267</v>
+        <v>-0.0208</v>
       </c>
       <c r="V3" t="n">
-        <v>0.8195</v>
+        <v>-0.7312</v>
       </c>
       <c r="W3" t="n">
-        <v>1.2186</v>
+        <v>0.8865</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.3991</v>
+        <v>-1.6177</v>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484215_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. RECIO PIÑOL</t>
+          <t>P. CARRIÓN SORIANO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.7595</v>
+        <v>1.521</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7629</v>
+        <v>1.521</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9966</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.9199000000000001</v>
+        <v>1.521</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3479</v>
+        <v>0.307</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.2679</v>
+        <v>1.214</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1039</v>
+        <v>1.521</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6971000000000001</v>
+        <v>0.307</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.5931999999999999</v>
+        <v>1.214</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.0239</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.3492</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.6747</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1953</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.1721</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0.9334</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7491</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1843</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.5507</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8865</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0.6642</v>
+        <v>0</v>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484215_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>F. VILAR FERNANDEZ</t>
+          <t>A. RECIO PINOL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6834</v>
+        <v>1.4525</v>
       </c>
       <c r="E5" t="n">
-        <v>3.6676</v>
+        <v>0.4559</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.9842</v>
+        <v>0.9966</v>
       </c>
       <c r="G5" t="n">
-        <v>3.6527</v>
+        <v>-1.2269</v>
       </c>
       <c r="H5" t="n">
-        <v>4.7324</v>
+        <v>0.0409</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.0797</v>
+        <v>-1.2679</v>
       </c>
       <c r="J5" t="n">
-        <v>5.5612</v>
+        <v>-0.203</v>
       </c>
       <c r="K5" t="n">
-        <v>4.7519</v>
+        <v>0.3901</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8093</v>
+        <v>-0.5931999999999999</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.9085</v>
+        <v>-1.0239</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0194</v>
+        <v>-0.3492</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.8891</v>
+        <v>-0.6747</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.3674</v>
+        <v>0.1953</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.9301</v>
+        <v>-0.9767</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5627</v>
+        <v>1.1721</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1293</v>
+        <v>0.9334</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1501</v>
+        <v>0.7491</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0208</v>
+        <v>0.1843</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.7312</v>
+        <v>1.5507</v>
       </c>
       <c r="W5" t="n">
         <v>0.8865</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.6177</v>
+        <v>0.6642</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484215_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -870,437 +895,462 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0547</v>
+        <v>1.221</v>
       </c>
       <c r="E6" t="n">
-        <v>1.6932</v>
+        <v>1.221</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.6385</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.8159</v>
+        <v>1.221</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3446</v>
+        <v>0.614</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.1605</v>
+        <v>0.607</v>
       </c>
       <c r="J6" t="n">
-        <v>1.2272</v>
+        <v>1.221</v>
       </c>
       <c r="K6" t="n">
-        <v>0.4988</v>
+        <v>0.614</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7284</v>
+        <v>0.607</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.0431</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.1542</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.8889</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>0.586</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.5395</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>1.1171</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>1.0333</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0838</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>0.1675</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.3862</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484215_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>G. HERETER MARCHANTE</t>
+          <t>P. CARRION SORIANO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0256</v>
+        <v>1.1111</v>
       </c>
       <c r="E7" t="n">
-        <v>1.9969</v>
+        <v>1.1081</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.9714</v>
+        <v>0.003</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7566000000000001</v>
+        <v>0.639</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3118</v>
+        <v>0.6127</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4447</v>
+        <v>0.0263</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6365</v>
+        <v>1.8683</v>
       </c>
       <c r="K7" t="n">
-        <v>0.596</v>
+        <v>0.4924</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0405</v>
+        <v>1.3758</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1201</v>
+        <v>-1.2293</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2842</v>
+        <v>0.1203</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4043</v>
+        <v>-1.3496</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.9767</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q7" t="n">
         <v>-1.9534</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9767</v>
+        <v>1.7581</v>
       </c>
       <c r="S7" t="n">
-        <v>0.9685</v>
+        <v>-0.152</v>
       </c>
       <c r="T7" t="n">
-        <v>0.9314</v>
+        <v>-0.0254</v>
       </c>
       <c r="U7" t="n">
-        <v>0.037</v>
+        <v>-0.1267</v>
       </c>
       <c r="V7" t="n">
-        <v>0.2772</v>
+        <v>0.8195</v>
       </c>
       <c r="W7" t="n">
-        <v>2.3824</v>
+        <v>1.2186</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.1052</v>
+        <v>-0.3991</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484215_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. JAIME BATLLE</t>
+          <t>G. HERETER MARCHANTE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7514999999999999</v>
+        <v>1.0256</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7425</v>
+        <v>1.9969</v>
       </c>
       <c r="F8" t="n">
-        <v>0.008999999999999999</v>
+        <v>-0.9714</v>
       </c>
       <c r="G8" t="n">
-        <v>1.2833</v>
+        <v>0.7566000000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.9824000000000001</v>
+        <v>0.3118</v>
       </c>
       <c r="I8" t="n">
-        <v>2.2657</v>
+        <v>0.4447</v>
       </c>
       <c r="J8" t="n">
-        <v>2.9971</v>
+        <v>0.6365</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.7534</v>
+        <v>0.596</v>
       </c>
       <c r="L8" t="n">
-        <v>3.7505</v>
+        <v>0.0405</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.7137</v>
+        <v>0.1201</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.2289</v>
+        <v>-0.2842</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.4848</v>
+        <v>0.4043</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q8" t="n">
         <v>-1.9534</v>
       </c>
       <c r="R8" t="n">
-        <v>1.9534</v>
+        <v>0.9767</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.41</v>
+        <v>0.9685</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3012</v>
+        <v>0.9314</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1088</v>
+        <v>0.037</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.1219</v>
+        <v>0.2772</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>2.3824</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.1219</v>
+        <v>-2.1052</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484215_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P. GARCIA RODRIGUEZ</t>
+          <t>A. JAIME BATLLE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2734</v>
+        <v>0.7514999999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2176</v>
+        <v>0.7425</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0558</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.3593</v>
+        <v>1.2833</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.4671</v>
+        <v>-0.9824000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1078</v>
+        <v>2.2657</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0552</v>
+        <v>2.9971</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.5921999999999999</v>
+        <v>-0.7534</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6475</v>
+        <v>3.7505</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.4146</v>
+        <v>-1.7137</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1251</v>
+        <v>-0.2289</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.5397</v>
+        <v>-1.4848</v>
       </c>
       <c r="P9" t="n">
-        <v>0.586</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-1.9534</v>
       </c>
       <c r="R9" t="n">
-        <v>0.586</v>
+        <v>1.9534</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0467</v>
+        <v>-0.41</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1624</v>
+        <v>-0.3012</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1156</v>
+        <v>-0.1088</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-0.1219</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.1219</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484215_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. PUERTAS GARCIA</t>
+          <t>A. RECIO PIÑOL</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.5657</v>
+        <v>0.307</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.4852</v>
+        <v>0.307</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.0804</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0.7739</v>
+        <v>0.307</v>
       </c>
       <c r="H10" t="n">
-        <v>1.8803</v>
+        <v>0.307</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.1064</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>3.1567</v>
+        <v>0.307</v>
       </c>
       <c r="K10" t="n">
-        <v>2.374</v>
+        <v>0.307</v>
       </c>
       <c r="L10" t="n">
-        <v>0.7827</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.3828</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.4937</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.8891</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.9301</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.9069</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9767</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1031</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0123</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1154</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>0.4875</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0.2102</v>
+        <v>0</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484215_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S. IBORRA BARRERA</t>
+          <t>P. GARCIA RODRIGUEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.0571</v>
+        <v>0.2734</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.7571</v>
+        <v>0.2176</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.3</v>
+        <v>0.0558</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.9167999999999999</v>
+        <v>-0.3593</v>
       </c>
       <c r="H11" t="n">
-        <v>0.8631</v>
+        <v>-0.4671</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.7799</v>
+        <v>0.1078</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.6368</v>
+        <v>0.0552</v>
       </c>
       <c r="K11" t="n">
-        <v>0.738</v>
+        <v>-0.5921999999999999</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.3748</v>
+        <v>0.6475</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.2799</v>
+        <v>-0.4146</v>
       </c>
       <c r="N11" t="n">
         <v>0.1251</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.4051</v>
+        <v>-0.5397</v>
       </c>
       <c r="P11" t="n">
         <v>0.586</v>
@@ -1312,418 +1362,444 @@
         <v>0.586</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3859</v>
+        <v>0.0467</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1203</v>
+        <v>0.1624</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2656</v>
+        <v>-0.1156</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.3405</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.3405</v>
+        <v>0</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484215_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>M. SUAREZ CANOSA</t>
+          <t>A. ABELLO GIRVES</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.5327</v>
+        <v>-0.1663</v>
       </c>
       <c r="E12" t="n">
-        <v>0.2732</v>
+        <v>0.4722</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.8059</v>
+        <v>-0.6385</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.6126</v>
+        <v>-2.0369</v>
       </c>
       <c r="H12" t="n">
-        <v>0.1023</v>
+        <v>-0.2694</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.715</v>
+        <v>-1.7675</v>
       </c>
       <c r="J12" t="n">
-        <v>0.137</v>
+        <v>0.0062</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0422</v>
+        <v>-0.1152</v>
       </c>
       <c r="L12" t="n">
-        <v>0.09470000000000001</v>
+        <v>0.1214</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.7496</v>
+        <v>-2.0431</v>
       </c>
       <c r="N12" t="n">
-        <v>0.0601</v>
+        <v>-0.1542</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.8097</v>
+        <v>-1.8889</v>
       </c>
       <c r="P12" t="n">
-        <v>0.1953</v>
+        <v>0.586</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-1.9534</v>
       </c>
       <c r="R12" t="n">
-        <v>0.1953</v>
+        <v>2.5395</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0447</v>
+        <v>1.1171</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.141</v>
+        <v>1.0333</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1856</v>
+        <v>0.0838</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.16</v>
+        <v>0.1675</v>
       </c>
       <c r="W12" t="n">
-        <v>0.2772</v>
+        <v>1.3862</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.4373</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484215_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>A. PUERTAS GARCIA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.572699999999999</v>
+        <v>-1.5657</v>
       </c>
       <c r="E13" t="n">
-        <v>11.4601</v>
+        <v>-0.4852</v>
       </c>
       <c r="F13" t="n">
-        <v>-4.8874</v>
+        <v>-1.0804</v>
       </c>
       <c r="G13" t="n">
-        <v>4.137799999999999</v>
+        <v>0.7739</v>
       </c>
       <c r="H13" t="n">
-        <v>8.186199999999999</v>
+        <v>1.8803</v>
       </c>
       <c r="I13" t="n">
-        <v>-4.0486</v>
+        <v>-1.1064</v>
       </c>
       <c r="J13" t="n">
-        <v>15.7783</v>
+        <v>3.1567</v>
       </c>
       <c r="K13" t="n">
-        <v>9.030299999999999</v>
+        <v>2.374</v>
       </c>
       <c r="L13" t="n">
-        <v>6.747999999999999</v>
+        <v>0.7827</v>
       </c>
       <c r="M13" t="n">
-        <v>-11.6405</v>
+        <v>-2.3828</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.8439000000000001</v>
+        <v>-0.4937</v>
       </c>
       <c r="O13" t="n">
-        <v>-10.7966</v>
+        <v>-1.8891</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.9767999999999999</v>
+        <v>-2.9301</v>
       </c>
       <c r="Q13" t="n">
-        <v>-15.6273</v>
+        <v>-3.9069</v>
       </c>
       <c r="R13" t="n">
-        <v>14.6506</v>
+        <v>0.9767</v>
       </c>
       <c r="S13" t="n">
-        <v>3.4666</v>
+        <v>0.1031</v>
       </c>
       <c r="T13" t="n">
-        <v>3.3851</v>
+        <v>-0.0123</v>
       </c>
       <c r="U13" t="n">
-        <v>0.08129999999999996</v>
+        <v>0.1154</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.05500000000000016</v>
+        <v>0.4875</v>
       </c>
       <c r="W13" t="n">
-        <v>7.9239</v>
+        <v>0.2772</v>
       </c>
       <c r="X13" t="n">
-        <v>-7.978999999999999</v>
+        <v>0.2102</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484215_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. VIÑALLONGA GOMEZ</t>
+          <t>S. IBORRA BARRERA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>C.B. GRANOLLERS</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.8556</v>
+        <v>-2.0571</v>
       </c>
       <c r="E14" t="n">
-        <v>3.4349</v>
+        <v>-0.7571</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.5794</v>
+        <v>-1.3</v>
       </c>
       <c r="G14" t="n">
-        <v>3.4756</v>
+        <v>-0.9167999999999999</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.1655</v>
+        <v>0.8631</v>
       </c>
       <c r="I14" t="n">
-        <v>4.6411</v>
+        <v>-1.7799</v>
       </c>
       <c r="J14" t="n">
-        <v>5.9422</v>
+        <v>-0.6368</v>
       </c>
       <c r="K14" t="n">
-        <v>0.4912</v>
+        <v>0.738</v>
       </c>
       <c r="L14" t="n">
-        <v>5.451</v>
+        <v>-1.3748</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.4666</v>
+        <v>-0.2799</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.6567</v>
+        <v>0.1251</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.8099</v>
+        <v>-0.4051</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.5627</v>
+        <v>0.586</v>
       </c>
       <c r="Q14" t="n">
-        <v>-4.1022</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.5395</v>
+        <v>0.586</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.3308</v>
+        <v>-0.3859</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.233</v>
+        <v>-0.1203</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0978</v>
+        <v>-0.2656</v>
       </c>
       <c r="V14" t="n">
-        <v>1.2735</v>
+        <v>-1.3405</v>
       </c>
       <c r="W14" t="n">
-        <v>1.8279</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.5545</v>
+        <v>-1.3405</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484215_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>G. PRAT PRUNA</t>
+          <t>M. SUAREZ CANOSA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>C.B. GRANOLLERS</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.0974</v>
+        <v>-2.5327</v>
       </c>
       <c r="E15" t="n">
-        <v>1.715</v>
+        <v>0.2732</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.6175</v>
+        <v>-2.8059</v>
       </c>
       <c r="G15" t="n">
-        <v>-2.232</v>
+        <v>-0.6126</v>
       </c>
       <c r="H15" t="n">
-        <v>0.1</v>
+        <v>0.1023</v>
       </c>
       <c r="I15" t="n">
-        <v>-2.332</v>
+        <v>-0.715</v>
       </c>
       <c r="J15" t="n">
-        <v>0.5741000000000001</v>
+        <v>0.137</v>
       </c>
       <c r="K15" t="n">
-        <v>1.8265</v>
+        <v>0.0422</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.2525</v>
+        <v>0.09470000000000001</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.8061</v>
+        <v>-0.7496</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.7265</v>
+        <v>0.0601</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.0795</v>
+        <v>-0.8097</v>
       </c>
       <c r="P15" t="n">
-        <v>1.3674</v>
+        <v>0.1953</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.1721</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.5395</v>
+        <v>0.1953</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.7524999999999999</v>
+        <v>0.0447</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4015</v>
+        <v>-0.141</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3509</v>
+        <v>0.1856</v>
       </c>
       <c r="V15" t="n">
-        <v>2.7145</v>
+        <v>-2.16</v>
       </c>
       <c r="W15" t="n">
-        <v>2.7145</v>
+        <v>0.2772</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-2.4373</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484215_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. MURCIANO PUJADAS</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>C.B. GRANOLLERS</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8397</v>
+        <v>6.572699999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>1.6629</v>
+        <v>11.4601</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.8232</v>
+        <v>-4.8874</v>
       </c>
       <c r="G16" t="n">
-        <v>0.3273</v>
+        <v>4.1379</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.3448</v>
+        <v>8.186199999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>1.6721</v>
+        <v>-4.0485</v>
       </c>
       <c r="J16" t="n">
-        <v>3.2633</v>
+        <v>15.7785</v>
       </c>
       <c r="K16" t="n">
-        <v>0.5116000000000001</v>
+        <v>9.030299999999999</v>
       </c>
       <c r="L16" t="n">
-        <v>2.7517</v>
+        <v>6.747999999999999</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.936</v>
+        <v>-11.6405</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.8565</v>
+        <v>-0.8439000000000001</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.0795</v>
+        <v>-10.7966</v>
       </c>
       <c r="P16" t="n">
-        <v>0.586</v>
+        <v>-0.9767999999999999</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.9534</v>
+        <v>-15.6273</v>
       </c>
       <c r="R16" t="n">
-        <v>2.5395</v>
+        <v>14.6506</v>
       </c>
       <c r="S16" t="n">
-        <v>0.4808</v>
+        <v>3.4666</v>
       </c>
       <c r="T16" t="n">
-        <v>0.353</v>
+        <v>3.3851</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1278</v>
+        <v>0.08129999999999998</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.5545</v>
+        <v>-0.05500000000000016</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>7.9239</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.5545</v>
-      </c>
+        <v>-7.978999999999999</v>
+      </c>
+      <c r="Y16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>F. REYES ARANDA</t>
+          <t>A. VIÑALLONGA GOMEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,31 +1811,31 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1753</v>
+        <v>2.7349</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.0201</v>
+        <v>2.7349</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1953</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0405</v>
+        <v>2.7349</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>0.307</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0405</v>
+        <v>2.4279</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0405</v>
+        <v>2.7349</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>0.307</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0405</v>
+        <v>2.4279</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -1771,19 +1847,19 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>0.1953</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.1953</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0605</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0605</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -1796,12 +1872,17 @@
       </c>
       <c r="X17" t="n">
         <v>0</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484215_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. TORNÉ DELAURENS</t>
+          <t>G. PRAT PRUNA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1894,78 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1088</v>
+        <v>1.0974</v>
       </c>
       <c r="E18" t="n">
-        <v>1.1162</v>
+        <v>1.715</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.2249</v>
+        <v>-0.6175</v>
       </c>
       <c r="G18" t="n">
-        <v>0.4539</v>
+        <v>-2.232</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1576</v>
+        <v>0.1</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2963</v>
+        <v>-2.332</v>
       </c>
       <c r="J18" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.5741000000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>0.6562</v>
+        <v>1.8265</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1619</v>
+        <v>-1.2525</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.3641</v>
+        <v>-2.8061</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.4986</v>
+        <v>-1.7265</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1344</v>
+        <v>-1.0795</v>
       </c>
       <c r="P18" t="n">
-        <v>0.3907</v>
+        <v>1.3674</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.1721</v>
       </c>
       <c r="R18" t="n">
-        <v>0.3907</v>
+        <v>2.5395</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.9533</v>
+        <v>-0.7524999999999999</v>
       </c>
       <c r="T18" t="n">
-        <v>0.07580000000000001</v>
+        <v>-0.4015</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.0291</v>
+        <v>-0.3509</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>2.7145</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2224</v>
+        <v>2.7145</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.2224</v>
+        <v>0</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484215_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>O. HERAS FLECHA</t>
+          <t>A. MURCIANO PUJADAS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1977,78 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.6329</v>
+        <v>0.8397</v>
       </c>
       <c r="E19" t="n">
-        <v>1.3547</v>
+        <v>1.6629</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.9876</v>
+        <v>-0.8232</v>
       </c>
       <c r="G19" t="n">
-        <v>5.0028</v>
+        <v>0.3273</v>
       </c>
       <c r="H19" t="n">
-        <v>0.4705</v>
+        <v>-1.3448</v>
       </c>
       <c r="I19" t="n">
-        <v>4.5324</v>
+        <v>1.6721</v>
       </c>
       <c r="J19" t="n">
-        <v>5.4417</v>
+        <v>3.2633</v>
       </c>
       <c r="K19" t="n">
-        <v>1.0438</v>
+        <v>0.5116000000000001</v>
       </c>
       <c r="L19" t="n">
-        <v>4.3979</v>
+        <v>2.7517</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.4388</v>
+        <v>-2.936</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.5733</v>
+        <v>-1.8565</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1344</v>
+        <v>-1.0795</v>
       </c>
       <c r="P19" t="n">
-        <v>-2.7348</v>
+        <v>0.586</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.9069</v>
+        <v>-1.9534</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1721</v>
+        <v>2.5395</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.073</v>
+        <v>0.4808</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1801</v>
+        <v>0.353</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.8929</v>
+        <v>0.1278</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.8279</v>
+        <v>-0.5545</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.8279</v>
+        <v>-0.5545</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484215_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>C. HOMS LORENZO</t>
+          <t>F. REYES ARANDA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +2060,78 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.0806</v>
+        <v>0.1753</v>
       </c>
       <c r="E20" t="n">
-        <v>0.5073</v>
+        <v>-0.0201</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.5879</v>
+        <v>0.1953</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.3521</v>
+        <v>0.0405</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.7872</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.5649</v>
+        <v>0.0405</v>
       </c>
       <c r="J20" t="n">
-        <v>0.5744</v>
+        <v>0.0405</v>
       </c>
       <c r="K20" t="n">
-        <v>0.2507</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0.3237</v>
+        <v>0.0405</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.9265</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.0379</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.8887</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1.7581</v>
+        <v>0.1953</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1721</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.9301</v>
+        <v>0.1953</v>
       </c>
       <c r="S20" t="n">
-        <v>0.7869</v>
+        <v>-0.0605</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.004</v>
+        <v>-0.0605</v>
       </c>
       <c r="U20" t="n">
-        <v>0.7909</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.2735</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.1089</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.3824</v>
+        <v>0</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484215_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. JUAREZ GIMENEZ</t>
+          <t>A. VINALLONGA GOMEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2143,78 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.0788</v>
+        <v>0.1206</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.5166</v>
+        <v>0.7</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.5622</v>
+        <v>-0.5794</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.2273</v>
+        <v>0.7407</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.715</v>
+        <v>-1.4725</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.5122</v>
+        <v>2.2132</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.6631</v>
+        <v>3.2073</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.6908</v>
+        <v>0.1842</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0276</v>
+        <v>3.0231</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.5641</v>
+        <v>-2.4666</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.0243</v>
+        <v>-1.6567</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.5399</v>
+        <v>-0.8099</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.1953</v>
+        <v>-1.5627</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1721</v>
+        <v>-4.1022</v>
       </c>
       <c r="R21" t="n">
-        <v>0.9767</v>
+        <v>2.5395</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.379</v>
+        <v>-0.3308</v>
       </c>
       <c r="T21" t="n">
-        <v>0.3186</v>
+        <v>-0.233</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.6976</v>
+        <v>-0.0978</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.2772</v>
+        <v>1.2735</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.8279</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.2772</v>
+        <v>-0.5545</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484215_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. SALMERON SEGU</t>
+          <t>M. TORNE DELAURENS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2226,78 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.1547</v>
+        <v>-0.1088</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.7451</v>
+        <v>1.1162</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.4096</v>
+        <v>-1.2249</v>
       </c>
       <c r="G22" t="n">
-        <v>-5.1224</v>
+        <v>0.4539</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.5869</v>
+        <v>0.1576</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.5355</v>
+        <v>0.2963</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.4706</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.2843</v>
+        <v>0.6562</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.1863</v>
+        <v>0.1619</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.6518</v>
+        <v>-0.3641</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.3026</v>
+        <v>-0.4986</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.3492</v>
+        <v>0.1344</v>
       </c>
       <c r="P22" t="n">
-        <v>0.9767</v>
+        <v>0.3907</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1721</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.1488</v>
+        <v>0.3907</v>
       </c>
       <c r="S22" t="n">
-        <v>0.1631</v>
+        <v>-0.9533</v>
       </c>
       <c r="T22" t="n">
-        <v>0.0696</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0935</v>
+        <v>-1.0291</v>
       </c>
       <c r="V22" t="n">
-        <v>1.8279</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.8279</v>
+        <v>0.2224</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-0.2224</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484215_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. PEIRO COSMO</t>
+          <t>O. HERAS FLECHA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2309,78 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.3634</v>
+        <v>-0.6329</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.8873</v>
+        <v>1.3547</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.4761</v>
+        <v>-1.9876</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.4253</v>
+        <v>5.0028</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.6408</v>
+        <v>0.4705</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2156</v>
+        <v>4.5324</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.2059</v>
+        <v>5.4417</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.2868</v>
+        <v>1.0438</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0809</v>
+        <v>4.3979</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.2194</v>
+        <v>-0.4388</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.354</v>
+        <v>-0.5733</v>
       </c>
       <c r="O23" t="n">
-        <v>0.1346</v>
+        <v>0.1344</v>
       </c>
       <c r="P23" t="n">
-        <v>0.1953</v>
+        <v>-2.7348</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-3.9069</v>
       </c>
       <c r="R23" t="n">
-        <v>0.1953</v>
+        <v>1.1721</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.5241</v>
+        <v>-1.073</v>
       </c>
       <c r="T23" t="n">
-        <v>0.0413</v>
+        <v>-0.1801</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.5655</v>
+        <v>-0.8929</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.6093</v>
+        <v>-1.8279</v>
       </c>
       <c r="W23" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.8865</v>
+        <v>-1.8279</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484215_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>M. BALLÚS TORRAS</t>
+          <t>C. HOMS LORENZO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2392,78 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.4473</v>
+        <v>-1.0806</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.7346</v>
+        <v>0.5073</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.7127</v>
+        <v>-1.5879</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.0788</v>
+        <v>-2.3521</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.6741</v>
+        <v>-0.7872</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.4047</v>
+        <v>-1.5649</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.6741</v>
+        <v>0.5744</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.6741</v>
+        <v>0.2507</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>0.3237</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.4047</v>
+        <v>-2.9265</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>-1.0379</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.4047</v>
+        <v>-1.8887</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>1.7581</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>-1.1721</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>2.9301</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.15</v>
+        <v>0.7869</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.0605</v>
+        <v>-0.004</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.08939999999999999</v>
+        <v>0.7909</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.2186</v>
+        <v>-1.2735</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.1089</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.2186</v>
+        <v>-2.3824</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484215_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>J. JUAREZ GIMENEZ</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,68 +2475,401 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.8985</v>
+        <v>-2.0788</v>
       </c>
       <c r="E25" t="n">
+        <v>-1.5166</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-0.5622</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-1.2273</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-0.715</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-0.5122</v>
+      </c>
+      <c r="J25" t="n">
+        <v>-0.6631</v>
+      </c>
+      <c r="K25" t="n">
+        <v>-0.6908</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.0276</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-0.5641</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-0.0243</v>
+      </c>
+      <c r="O25" t="n">
+        <v>-0.5399</v>
+      </c>
+      <c r="P25" t="n">
+        <v>-0.1953</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>-1.1721</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0.9767</v>
+      </c>
+      <c r="S25" t="n">
+        <v>-0.379</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0.3186</v>
+      </c>
+      <c r="U25" t="n">
+        <v>-0.6976</v>
+      </c>
+      <c r="V25" t="n">
+        <v>-0.2772</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>-0.2772</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_2484215_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>M. SALMERON SEGU</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>C.B. GRANOLLERS</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>-2.1547</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-1.7451</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-0.4096</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-5.1224</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-2.5869</v>
+      </c>
+      <c r="I26" t="n">
+        <v>-2.5355</v>
+      </c>
+      <c r="J26" t="n">
+        <v>-2.4706</v>
+      </c>
+      <c r="K26" t="n">
+        <v>-1.2843</v>
+      </c>
+      <c r="L26" t="n">
+        <v>-1.1863</v>
+      </c>
+      <c r="M26" t="n">
+        <v>-2.6518</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-1.3026</v>
+      </c>
+      <c r="O26" t="n">
+        <v>-1.3492</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0.9767</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>-1.1721</v>
+      </c>
+      <c r="R26" t="n">
+        <v>2.1488</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0.1631</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0.0696</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0.0935</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.8279</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.8279</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_2484215_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>A. PEIRO COSMO</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>C.B. GRANOLLERS</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
+        <v>-2.3634</v>
+      </c>
+      <c r="E27" t="n">
+        <v>-0.8873</v>
+      </c>
+      <c r="F27" t="n">
+        <v>-1.4761</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-1.4253</v>
+      </c>
+      <c r="H27" t="n">
+        <v>-1.6408</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.2156</v>
+      </c>
+      <c r="J27" t="n">
+        <v>-1.2059</v>
+      </c>
+      <c r="K27" t="n">
+        <v>-1.2868</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0.0809</v>
+      </c>
+      <c r="M27" t="n">
+        <v>-0.2194</v>
+      </c>
+      <c r="N27" t="n">
+        <v>-0.354</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0.1346</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0.1953</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0.1953</v>
+      </c>
+      <c r="S27" t="n">
+        <v>-0.5241</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0.0413</v>
+      </c>
+      <c r="U27" t="n">
+        <v>-0.5655</v>
+      </c>
+      <c r="V27" t="n">
+        <v>-0.6093</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0.2772</v>
+      </c>
+      <c r="X27" t="n">
+        <v>-0.8865</v>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>play_by_play_2484215_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>M. BALLUS TORRAS</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>C.B. GRANOLLERS</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="n">
+        <v>-2.4473</v>
+      </c>
+      <c r="E28" t="n">
+        <v>-0.7346</v>
+      </c>
+      <c r="F28" t="n">
+        <v>-1.7127</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-1.0788</v>
+      </c>
+      <c r="H28" t="n">
+        <v>-0.6741</v>
+      </c>
+      <c r="I28" t="n">
+        <v>-0.4047</v>
+      </c>
+      <c r="J28" t="n">
+        <v>-0.6741</v>
+      </c>
+      <c r="K28" t="n">
+        <v>-0.6741</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>-0.4047</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>-0.4047</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="T28" t="n">
+        <v>-0.0605</v>
+      </c>
+      <c r="U28" t="n">
+        <v>-0.08939999999999999</v>
+      </c>
+      <c r="V28" t="n">
+        <v>-1.2186</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" t="n">
+        <v>-1.2186</v>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>play_by_play_2484215_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>C.B. GRANOLLERS</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" t="n">
+        <v>-5.898599999999999</v>
+      </c>
+      <c r="E29" t="n">
         <v>4.887300000000001</v>
       </c>
-      <c r="F25" t="n">
+      <c r="F29" t="n">
         <v>-10.7858</v>
       </c>
-      <c r="G25" t="n">
+      <c r="G29" t="n">
         <v>-4.1378</v>
       </c>
-      <c r="H25" t="n">
+      <c r="H29" t="n">
         <v>-8.186199999999999</v>
       </c>
-      <c r="I25" t="n">
-        <v>4.0487</v>
-      </c>
-      <c r="J25" t="n">
+      <c r="I29" t="n">
+        <v>4.048700000000001</v>
+      </c>
+      <c r="J29" t="n">
         <v>11.6405</v>
       </c>
-      <c r="K25" t="n">
+      <c r="K29" t="n">
         <v>0.844</v>
       </c>
-      <c r="L25" t="n">
+      <c r="L29" t="n">
         <v>10.7964</v>
       </c>
-      <c r="M25" t="n">
+      <c r="M29" t="n">
         <v>-15.7781</v>
       </c>
-      <c r="N25" t="n">
+      <c r="N29" t="n">
         <v>-9.0304</v>
       </c>
-      <c r="O25" t="n">
+      <c r="O29" t="n">
         <v>-6.748</v>
       </c>
-      <c r="P25" t="n">
-        <v>0.9766999999999999</v>
-      </c>
-      <c r="Q25" t="n">
+      <c r="P29" t="n">
+        <v>0.9767</v>
+      </c>
+      <c r="Q29" t="n">
         <v>-14.6509</v>
       </c>
-      <c r="R25" t="n">
+      <c r="R29" t="n">
         <v>15.6275</v>
       </c>
-      <c r="S25" t="n">
+      <c r="S29" t="n">
         <v>-2.792399999999999</v>
       </c>
-      <c r="T25" t="n">
+      <c r="T29" t="n">
         <v>-0.08130000000000009</v>
       </c>
-      <c r="U25" t="n">
+      <c r="U29" t="n">
         <v>-2.711</v>
       </c>
-      <c r="V25" t="n">
+      <c r="V29" t="n">
         <v>0.05490000000000061</v>
       </c>
-      <c r="W25" t="n">
+      <c r="W29" t="n">
         <v>7.978800000000001</v>
       </c>
-      <c r="X25" t="n">
+      <c r="X29" t="n">
         <v>-7.923999999999999</v>
       </c>
+      <c r="Y29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
